--- a/integration-tests/fixtures/rendering.xlsx
+++ b/integration-tests/fixtures/rendering.xlsx
@@ -1,6 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Notes" sheetId="2" r:id="rId3"/>
